--- a/ITS-237-Project-details.xlsx
+++ b/ITS-237-Project-details.xlsx
@@ -2795,7 +2795,7 @@
       <c r="A14" s="117" t="inlineStr">
         <is>
           <t>Deploy an enterprise automated Microsoft Teams Calling Bot (TDA Bot) that automatically attends enterprise meetings, captures real-time unmixed audio and synchronized video feeds via Microsoft Graph Calling SDK and Skype Media Platform, transcribes speech with speaker diarization using OpenAI Whisper, and generates structured Minutes of Meeting (MoM) documents in Word (.docx) format delivered directly to meeting organizers.
-The solution eliminates manual note-taking overhead (saving 2-4 hours per meeting), ensures 100% compliance recording, centralizes meeting knowledge in Google Cloud Storage (GCS) and Google BigQuery, and supports seamless command-based control (@TDA #joinv2, #status, #stop, #leave) with real-time visual recording mascot status feedback.</t>
+The system is engineered for enterprise scale, supporting 100 concurrent meetings and 1,000 daily meetings across Tata Steel. The solution eliminates manual note-taking overhead (saving 2,000 - 4,000 employee hours daily across 1,000 meetings), ensures 100% compliance recording, centralizes meeting knowledge in Google Cloud Storage (GCS) and Google BigQuery, and supports seamless command-based control (@TDA #joinv2, #status, #stop, #leave) with real-time visual mascot status feedback.</t>
         </is>
       </c>
       <c r="B14" s="183" t="n"/>
@@ -2925,8 +2925,8 @@
 5. Automated speech-to-text pipeline utilizing OpenAI Whisper with multi-speaker diarization and timeline synchronization.
 6. LLM-powered MoM summarizer generating executive summaries, discussion points, and action items in Microsoft Word (.docx) format within 5 minutes.
 7. Secure archival of audio, video, transcripts, and MoM files in Google Cloud Storage (GCS) with BigQuery audit telemetry.
-8. High-concurrency architecture supporting up to 100 concurrent calls with Google Cloud Firestore distributed locks.
-9. Comprehensive Information Security controls: tenant isolation, SRTP media encryption, TLS 1.3, mTLS certificate authentication, zero persistent local VM media storage.</t>
+8. High-concurrency enterprise architecture supporting up to 100 concurrent meetings and 1,000 daily meetings with Google Cloud Firestore distributed locks.
+9. Comprehensive Information Security controls: tenant isolation, SRTP media encryption, TLS 1.3, mTLS certificate authentication, zero persistent local VM media storage (immediate purge post-GCS upload).</t>
         </is>
       </c>
       <c r="B16" s="183" t="n"/>
@@ -3110,8 +3110,8 @@
     <row r="18" ht="106.5" customHeight="1">
       <c r="A18" s="117" t="inlineStr">
         <is>
-          <t>Tata Steel employees and leadership conduct hundreds of critical operational reviews, governance committees, and cross-functional project meetings daily. Manual note-taking is inconsistent, error-prone, and delays action item tracking by days. Previous browser-based bots (e.g. Playwright / headless Chromium) suffered from severe latency (&gt;30-45 seconds join time), audio stutter, high resource contention, and lacked individual speaker audio separation.
-The Teams Calling Bot (TDA Bot) utilizes the native Microsoft Graph Communications Calling SDK and Skype Media Platform to provide sub-3-second join times, isolated unmixed PCM audio per speaker, high-reliability video recording, and immediate automated MoM delivery with enterprise-grade security.</t>
+          <t>Tata Steel employees and leadership conduct hundreds of critical operational reviews, governance committees, and cross-functional project meetings daily, scaling up to 1,000 daily meetings enterprise-wide. Manual note-taking is inconsistent, labor-intensive (costing 2-4 hours per meeting), and delays action item tracking by days. Previous browser-based bots (e.g. Playwright / headless Chromium) suffered from severe latency (&gt;30-45 seconds join time), audio stutter, high resource contention, and could not scale past 5 concurrent calls.
+The Teams Calling Bot (TDA Bot) utilizes native Microsoft Graph Communications Calling SDK and Skype Media Platform to provide sub-3-second join times, isolated unmixed PCM audio per speaker, high-reliability video recording, robust capacity for 100 concurrent meetings and 1,000 daily meetings, and immediate automated MoM delivery with enterprise-grade security.</t>
         </is>
       </c>
       <c r="B18" s="183" t="n"/>
@@ -3337,7 +3337,7 @@
       <c r="G22" s="118" t="inlineStr">
         <is>
           <t>1. Bot Join Latency: Baseline = 30-45s (browser-based bot) | Target = &lt; 3.0s (Calling SDK native join).
-2. Concurrency Capacity: Baseline = 5 calls | Target = 100 concurrent meetings on VM cluster.
+2. Concurrency &amp; Daily Throughput: Baseline = 5 calls | Target = 100 concurrent meetings and 1,000 daily meetings processed on VM cluster.
 3. MoM Turnaround Time: Baseline = 2-4 hours manual | Target = &lt; 5 minutes automated post-call.
 4. Audio &amp; Video Quality: Baseline = mixed low-quality audio | Target = 16kHz unmixed PCM audio &amp; 720p/1080p video.
 5. System Availability / Uptime: Baseline = 95.0% | Target = 99.9% uptime with automated health checks.
@@ -3555,9 +3555,9 @@
 1. Call Join Latency: Bot must join scheduled or ad-hoc Teams meetings within 3.0 seconds of receiving @TDA #joinv2 command or calendar trigger.
 2. Visual Recording Transparency: Bot must broadcast a live mascot video stream throughout the call displaying recording status, meeting title, and active duration.
 3. Media Quality &amp; Completeness: Capture 100% of meeting audio as unmixed 16kHz 16-bit PCM streams per participant without clipping, dropouts, or downmixing distortion. Capture synchronized video up to 1080p.
-4. Scalability &amp; High Concurrency: Bot infrastructure must successfully support up to 100 concurrent meetings simultaneously with &lt; 1% CPU jitter and 99.9% uptime.
+4. Scalability &amp; High Concurrency: Bot infrastructure must successfully support up to 100 concurrent meetings simultaneously and a daily throughput of 1,000 meetings per day with &lt; 1% CPU jitter, &lt; 5 min MoM delivery, and 99.9% uptime.
 5. AI Transcription &amp; MoM Delivery: Automated Whisper transcription with speaker identification, followed by structured MoM generation in Word (.docx) format delivered to the organizer within 5 minutes of meeting termination.
-6. Cloud Archival &amp; Searchability: All meeting recordings, transcripts, and MoM summaries automatically archived in Google Cloud Storage with full metadata indexed in Google BigQuery.
+6. Cloud Archival &amp; Searchability: All meeting recordings, transcripts, and MoM summaries automatically archived in Google Cloud Storage with full metadata indexed in Google BigQuery (sized for 1,000 meetings/day).
 7. Infosec &amp; Security Assessment Compliance: Zero persistent raw media retention on local VM disk (automatic purge post-GCS upload); full SRTP media encryption; TLS 1.3 for all REST/webhook traffic; mTLS certificate authentication; strict Tata Steel tenant-only isolation.</t>
         </is>
       </c>
